--- a/模组列表.xlsx
+++ b/模组列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECABC40-9442-4773-8373-2D39C3D97C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0571EAE6-8732-4940-A13C-7534C01E9F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,10 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="423">
   <si>
     <t>原版名称</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>AetherAspects</t>
@@ -85,1137 +85,1137 @@
   </si>
   <si>
     <t>扩展/优化</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>其他模组</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Achgrate</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>修复模组联动的一些BUG</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>GTNH维护的模组的Lib库</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>1.7.10版本的Mixin总和</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>破坏性修复龙API和魔戒的冲突</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>EntityCulling-Unofficial</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>实体渲染机制优化</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：传承</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>LOTRMod</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">ChromatiCraft </t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Thaumcraft拓展 前置是DragonAPI </t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Middleearththaumaturgy</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>中土神秘学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是LOTRMod</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔戒nei附属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔戒合成</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家, NEI Recipe Handlers</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Aether</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Aether</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Gilded-games-util</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Gilded-games-util</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘生物要素扫描</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>TwilightForest</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>应用能源2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>天境2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>天境要素扫描</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>以太前置库</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>黑暗神秘学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>暮色森林</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>旅者之器</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘基础学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>SpecialMobs</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>特殊怪物</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>LycanitesMobsComplete</t>
   </si>
   <si>
     <t>恐怖生物</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>MoCreatures-Legacy-Final</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>更多生物分支版本</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>WitchingGadgets</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>巫师宝具</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumaturgical Knowledge</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>TravellersGear</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>WarpTheory</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘扭曲学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcarpentry</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘木匠</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘奥义</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThermalFoundation</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>热力基本</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThermalDynamics</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>热动力学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工艺</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>TofuFactoryR</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工厂重制版</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>林业</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>光明之弓</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔法蜜蜂</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Forestry</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是Forestry</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔法曲奇</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>混合魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>MagicalDecorations</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘装饰</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>自然魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>AdvancedThaumaturgy</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>炼金炉篦</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>高等神秘学2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代nei附属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftGates</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>奥法管道</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BC</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>源质罐子统计</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Polybius</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>更多要素</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>TCBotaniaExoflame</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Talismans2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>护身符2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Machina</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘工匠</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicUtilities</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘实用工具</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic_Upholstery</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumores</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>奥能矿物</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicSanity</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>扭曲修正</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicPipes</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘管道</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，MJUtils</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，nei全家</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Additions</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘领域</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ParticleLib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Dyes</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘染料</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘力学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Nexus</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicenergistics</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘能源</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Applied Energistics 2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicalchemy</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘炼金学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicEquivalence</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>奥法置换</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumichorizons</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘视界</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicInfusion</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘注魔</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExpansion</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘膨胀</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExploration</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘探险</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘守望者</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘启示</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔法金属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>量子魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>奥法工程学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ImmersiveEngineering</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneArteries</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>奥法献祭学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Automagy</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>自动化魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Carpenter's Blocks</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Avaritia</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>无尽贪婪</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>血魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>热力核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>CodeChickenCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>鸡块核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>木匠方块</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Carpenter's+Blocks</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>建筑核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>建筑</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是buildcraft-compat</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>植物魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>CraftArcanum</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔改</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ElectricThaum</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>电力魔法工具</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BloodMagic，EvilCraft，Botania</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ImmersiveEngineering</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ElecCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2，ElecCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>EssentialThaumaturgy</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>EssentialCraft3</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>源质神秘学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，EssentialCraft3</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是DummyCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Nihilo</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>无中生有</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Forbidden</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>禁忌魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ForgeMultipart</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Gadomancy</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔像秘经</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Hammerz</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>HeartWork</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>心血结晶</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>InfusionBrewing</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>注魔酿造</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>源质魔法3</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>沉浸工程</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>工业时代2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>IndustrialUpgrade</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>工业升级</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Industrialcraft</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Industrialcraft</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>InventoryTweaks</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>R键整理</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑艺术之刃</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade-SlashArts</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Symcalc</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>对称度运算仪</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>奥数投射</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>等价交换</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Railcraft</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>NodalMechanics</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>节点力学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Technomancy</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Tchelper</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘研究帮助</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Tcinventoryscan</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代物品栏扫描</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Tcnodetracker</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘节点追踪</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Tainted-Magic</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>污秽魔法</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>姆亚核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Shamanry</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>巫媒</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Origin</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ParticleLib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>粒子库</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>铁路</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>DummyCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>齿轮核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，DummyCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>锤子</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>OmnisCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>橘子核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Mjutils</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，PrjectE</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ExtraScepterStaff</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>独角兽权杖</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Boots</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘靴子</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Muya</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Ex-Nihilo</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Localization Optimizer</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代本地化优化</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Not Enough Thaumcraft Tabs</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>无限神秘标签页</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 Tweaks</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>失落遗物学</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Forgotten Relics</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Transmute Liquids</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘标签页</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>液体嬗变</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>星辉生万物重制版</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Astris-Rebirth</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Garden of Glass</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>水晶花园</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置Botania</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>FpsReducer</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Fps减速器</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Thermal热力全家，Origin</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>nei添加更多神秘合成类型显示</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘纠缠</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicBases</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicRevelations</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>AWWayofTime</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔法作物</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>区块预生成器</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>F</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Warden</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicTinkerer</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>IlluminatedBows</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>MagiaNaturalis</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>MagicCookies</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>MixedMagic</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>支持拼音搜索与 JEI 风格的关键字匹配</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneEngineering</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ElectroMagicTools</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>巫术</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Omnis Core，Multipart，CodeChicken Lib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，CodeChicken Lib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>格雷科技6</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>工艺奥秘,电力神秘</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>库</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft联动是TwilightForest,LycanitesMobsComplete,MoCreatures,SpecialMobs</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">  模组重置了NEI的注册系统会在根目录下写入缓存，模组变动一次就会重写一次。会导致加载时间变长很多。放在了可以替换模组的文件夹下。需要使用可以加载。</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>要点</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Aroma1997Core</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>AromaBackup</t>
   </si>
   <si>
     <t>Aroma系列模组核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>备份模组</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Aroma1997Core</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>EnderIO</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>高版本加载界面</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>EnderCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>末影核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>末影接口</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Angelica</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>替代optfine</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>NEI包括附属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Nei合成显示扩展</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>NEI-Integration</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>原版名称</t>
@@ -1231,475 +1231,506 @@
   </si>
   <si>
     <t>前置是Thaumcraft，旧版本译名神秘守望者，还有更古早的叫Thaumic Warden都是这个模组。</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>GregTech 6</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft   Thaumcraft 4 Tweaks类似功能</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Xaeros_Minimap</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Xaero的小地图</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Omnis核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘混成</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicHybrid</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘糅合</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，通过Mixin注入的方式修复了联动和神秘4本身的一些问题</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Integration</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘集合</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftAltarCull</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘祭坛稳定器渲染剔除</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，当玩家远离祭坛时，自动“剔除”稳定器方块 的渲染</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，将Thaumcraft模组的机制和要素整合进其他不原生支持 Thaumcraft 的模组里</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 : Patched</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4：修补</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，NemexLib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>NemexLib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Nemex库</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘温泉</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Renaissance</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘复兴</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是unimixins-all，DragonAPI ，LOTRMod，所有的材质都未实装</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Deathly Hallows</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>死亡圣器</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania，Witchery</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Essentia Pipes</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>管道简化</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Salis Arcana</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>奥秘之盐</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Cybersus</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔能义体</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ItemBlackListFIXED</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>物品黑名单修复版</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>合成冲突消除：修复版</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>RecipeConflict Fixer</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>ChromatiFixes</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：溢出修复</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，修复和其他模组可能导致的工具类数组溢出</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究前置</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>BrandonsCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Draconic-Evolution</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Hell Integrations</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘众戒</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Baubles Expanded和Baubles任选其一</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Avaritia，Botania，Applied Energistics 2，Draconic Evolution，Advanced Solar Panels</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置BrandonsCore</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑西风之刃</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>LOTweakR</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元修复</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元另一个修复</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">前置是ChromatiCraft </t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>安装可否</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Bugtorch</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Gtnhlib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>中文名/注释</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Modernsplash</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Unimixins-all</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft-compat</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Jar Checker</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>地狱合集</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>联动模组</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Trop</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicthermae</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicmixins</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Manametalmod</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Magicbees</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Witchery</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Neiaddons</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Nechar-GTNH（NotEnoughCharacters）</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Tcneiadditions</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Lotrcrashfix</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>NeiRecipeHandlers</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>NeiLotr</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Minus Thaumcraft</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Errata</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，联动了Grimoire of Gaia，Automagy，Thermal Foundation</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑包括附属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是SlashBlade</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade，SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Magicalcrops</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>以太2包括附属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>魔戒包括附属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元以及修复</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrialcraft，Tainted Magic，Electro Magic Tools（EMT）</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>神秘联动 1.1.2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑-暗鸦 1.1.2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>红色名字是作者反编译+修BUG后重新打包的模组。绿色名字是新加的模组后面是整合包版本号</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Chromaticraft-AIFixes（Zaifix）</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>JAOPC</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>另一版本的统一矿物</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>CarbonConfig</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator的核心</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是CarbonConfig</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>自动解锁所有神秘时代研究1.2.2</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>chunkapi</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>endlessids</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>我看到了什么</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>wdmla</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Wawla</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>waila的fork版本</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>拓展所有ID</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>falsepatternlib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>前置是chunkapi，falsepatternlib</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>对非 libraries 模组进行版本安全的依赖处理</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>将自定义数据添加到区块的模组</t>
-    <phoneticPr fontId="28" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>forgelin-GTNH</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置是Thaumcraft，forgelin-GTNH</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>ThaumcraftResearchTweaks</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>研究工具 1.1.6</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>forgelin</t>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1970,14 +2001,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="9"/>
@@ -1994,7 +2017,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2028,6 +2051,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2055,195 +2084,192 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2251,47 +2277,59 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2579,8 +2617,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M81"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14"/>
+  <dimension ref="A1:M82"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.75" style="3" customWidth="1"/>
     <col min="2" max="2" width="37.75" style="3" bestFit="1" customWidth="1"/>
@@ -2597,7 +2635,7 @@
     <col min="13" max="16384" width="8.9140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2636,7 +2674,7 @@
       </c>
       <c r="M1" s="5"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -2657,15 +2695,15 @@
       <c r="L2" s="4"/>
       <c r="M2" s="5"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>293</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="C3" s="75" t="s">
-        <v>258</v>
+      <c r="C3" s="74" t="s">
+        <v>419</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
@@ -2691,7 +2729,7 @@
       </c>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>283</v>
       </c>
@@ -2727,7 +2765,7 @@
       </c>
       <c r="M4" s="5"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>284</v>
       </c>
@@ -2766,7 +2804,7 @@
       </c>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>358</v>
       </c>
@@ -2801,20 +2839,20 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="13.75" customHeight="1">
+    <row r="7" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>399</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>400</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="67" t="s">
         <v>258</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="49" t="s">
         <v>137</v>
       </c>
       <c r="G7" s="16" t="s">
@@ -2837,7 +2875,7 @@
       </c>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="13.75" customHeight="1">
+    <row r="8" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>156</v>
       </c>
@@ -2876,7 +2914,7 @@
       </c>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
@@ -2912,7 +2950,7 @@
       </c>
       <c r="M9" s="5"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>251</v>
       </c>
@@ -2948,7 +2986,7 @@
       </c>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>359</v>
       </c>
@@ -2984,7 +3022,7 @@
       </c>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>353</v>
       </c>
@@ -3023,7 +3061,7 @@
       </c>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>361</v>
       </c>
@@ -3047,14 +3085,14 @@
       </c>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="72" t="s">
         <v>415</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="71" t="s">
         <v>258</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -3077,11 +3115,11 @@
       <c r="L14" s="4"/>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="68" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -3090,7 +3128,7 @@
       <c r="E15" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="49" t="s">
         <v>169</v>
       </c>
       <c r="G15" s="18" t="s">
@@ -3111,14 +3149,14 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="73" t="s">
         <v>416</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="71" t="s">
         <v>258</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -3147,14 +3185,14 @@
       </c>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="68" t="s">
         <v>412</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="71" t="s">
         <v>258</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -3186,7 +3224,7 @@
       </c>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:13" ht="14" customHeight="1">
+    <row r="18" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="3" t="s">
         <v>242</v>
       </c>
@@ -3207,7 +3245,7 @@
       <c r="L18" s="56"/>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
@@ -3239,11 +3277,11 @@
       </c>
       <c r="M19" s="5"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="66" t="s">
         <v>398</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -3268,7 +3306,7 @@
       <c r="L20"/>
       <c r="M20" s="5"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>2</v>
       </c>
@@ -3281,7 +3319,7 @@
       <c r="E21" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="49" t="s">
         <v>75</v>
       </c>
       <c r="G21" s="16" t="s">
@@ -3298,7 +3336,7 @@
       <c r="L21" s="4"/>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" spans="1:13" ht="13.75" customHeight="1">
+    <row r="22" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>144</v>
       </c>
@@ -3311,7 +3349,7 @@
       <c r="E22" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="49" t="s">
         <v>184</v>
       </c>
       <c r="G22" s="18" t="s">
@@ -3332,7 +3370,7 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>259</v>
       </c>
@@ -3345,7 +3383,7 @@
       <c r="E23" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="49" t="s">
         <v>83</v>
       </c>
       <c r="G23" s="16" t="s">
@@ -3368,7 +3406,7 @@
       </c>
       <c r="M23" s="5"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,7 +3419,7 @@
       <c r="E24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="49" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="16" t="s">
@@ -3404,7 +3442,7 @@
       </c>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>345</v>
       </c>
@@ -3428,7 +3466,7 @@
       </c>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>363</v>
       </c>
@@ -3461,7 +3499,7 @@
       <c r="L26" s="7"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>364</v>
       </c>
@@ -3497,7 +3535,7 @@
       </c>
       <c r="M27" s="5"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>151</v>
       </c>
@@ -3533,7 +3571,7 @@
       </c>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
@@ -3569,7 +3607,7 @@
       </c>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
@@ -3605,7 +3643,7 @@
       </c>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>5</v>
       </c>
@@ -3629,7 +3667,7 @@
       </c>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>346</v>
       </c>
@@ -3662,7 +3700,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="5"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>222</v>
       </c>
@@ -3698,7 +3736,7 @@
       </c>
       <c r="M33" s="5"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>165</v>
       </c>
@@ -3734,7 +3772,7 @@
       </c>
       <c r="M34" s="5"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>290</v>
       </c>
@@ -3770,7 +3808,7 @@
       </c>
       <c r="M35" s="5"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>288</v>
       </c>
@@ -3794,7 +3832,7 @@
       </c>
       <c r="M36" s="5"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>168</v>
       </c>
@@ -3827,7 +3865,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="5"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>173</v>
       </c>
@@ -3859,7 +3897,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>77</v>
       </c>
@@ -3895,7 +3933,7 @@
       </c>
       <c r="M39" s="5"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>177</v>
       </c>
@@ -3931,7 +3969,7 @@
       </c>
       <c r="M40" s="5"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>248</v>
       </c>
@@ -3970,7 +4008,7 @@
       </c>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>138</v>
       </c>
@@ -4006,7 +4044,7 @@
       </c>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>190</v>
       </c>
@@ -4030,7 +4068,7 @@
       </c>
       <c r="M43" s="5"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>188</v>
       </c>
@@ -4054,7 +4092,7 @@
       </c>
       <c r="M44" s="5"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>192</v>
       </c>
@@ -4081,7 +4119,7 @@
       </c>
       <c r="M45" s="5"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>336</v>
       </c>
@@ -4108,7 +4146,7 @@
       </c>
       <c r="M46" s="5"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>54</v>
       </c>
@@ -4118,13 +4156,13 @@
       <c r="C47" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E47" s="66" t="s">
+      <c r="E47" s="75" t="s">
         <v>380</v>
       </c>
-      <c r="F47" s="71" t="s">
+      <c r="F47" s="70" t="s">
         <v>402</v>
       </c>
-      <c r="G47" s="70" t="s">
+      <c r="G47" s="69" t="s">
         <v>262</v>
       </c>
       <c r="H47" s="3" t="s">
@@ -4132,7 +4170,7 @@
       </c>
       <c r="M47" s="5"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>228</v>
       </c>
@@ -4156,7 +4194,7 @@
       </c>
       <c r="M48" s="5"/>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>56</v>
       </c>
@@ -4180,7 +4218,7 @@
       </c>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>6</v>
       </c>
@@ -4204,7 +4242,7 @@
       </c>
       <c r="M50" s="5"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>7</v>
       </c>
@@ -4228,7 +4266,7 @@
       </c>
       <c r="M51" s="5"/>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>321</v>
       </c>
@@ -4238,21 +4276,21 @@
       <c r="C52" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="G52" s="15" t="s">
+      <c r="E52" s="75" t="s">
+        <v>420</v>
+      </c>
+      <c r="F52" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="G52" s="16" t="s">
         <v>258</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>112</v>
+        <v>418</v>
       </c>
       <c r="M52" s="5"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>226</v>
       </c>
@@ -4266,20 +4304,20 @@
         <v>410</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="G53" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G53" s="15" t="s">
         <v>258</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>392</v>
+        <v>112</v>
       </c>
       <c r="M53" s="5"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>218</v>
       </c>
@@ -4290,20 +4328,20 @@
         <v>258</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>97</v>
+        <v>232</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="G54" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G54" s="18" t="s">
         <v>258</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>27</v>
+        <v>392</v>
       </c>
       <c r="M54" s="5"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>219</v>
       </c>
@@ -4314,12 +4352,12 @@
         <v>258</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F55" s="44" t="s">
-        <v>325</v>
-      </c>
-      <c r="G55" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" s="14" t="s">
         <v>258</v>
       </c>
       <c r="H55" s="3" t="s">
@@ -4327,7 +4365,7 @@
       </c>
       <c r="M55" s="5"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>8</v>
       </c>
@@ -4338,20 +4376,20 @@
         <v>258</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F56" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="G56" s="18" t="s">
-        <v>262</v>
+        <v>324</v>
+      </c>
+      <c r="F56" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="G56" s="41" t="s">
+        <v>258</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>27</v>
       </c>
       <c r="M56" s="5"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>339</v>
       </c>
@@ -4362,20 +4400,20 @@
         <v>258</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F57" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>258</v>
+        <v>263</v>
+      </c>
+      <c r="F57" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>262</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>27</v>
       </c>
       <c r="M57" s="5"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>52</v>
       </c>
@@ -4385,13 +4423,13 @@
       <c r="C58" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E58" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="F58" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="G58" s="14" t="s">
+      <c r="E58" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="16" t="s">
         <v>258</v>
       </c>
       <c r="H58" s="3" t="s">
@@ -4399,7 +4437,7 @@
       </c>
       <c r="M58" s="5"/>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>69</v>
       </c>
@@ -4409,21 +4447,21 @@
       <c r="C59" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E59" s="58" t="s">
-        <v>256</v>
-      </c>
-      <c r="F59" s="38" t="s">
-        <v>51</v>
+      <c r="E59" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="F59" s="60" t="s">
+        <v>121</v>
       </c>
       <c r="G59" s="14" t="s">
         <v>258</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>224</v>
+        <v>27</v>
       </c>
       <c r="M59" s="5"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>67</v>
       </c>
@@ -4434,20 +4472,20 @@
         <v>258</v>
       </c>
       <c r="E60" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="38" t="s">
-        <v>48</v>
+        <v>256</v>
+      </c>
+      <c r="F60" s="78" t="s">
+        <v>51</v>
       </c>
       <c r="G60" s="14" t="s">
         <v>258</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>27</v>
+        <v>224</v>
       </c>
       <c r="M60" s="5"/>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>72</v>
       </c>
@@ -4457,11 +4495,11 @@
       <c r="C61" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F61" s="49" t="s">
-        <v>114</v>
+      <c r="E61" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>48</v>
       </c>
       <c r="G61" s="14" t="s">
         <v>258</v>
@@ -4471,7 +4509,7 @@
       </c>
       <c r="M61" s="5"/>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>61</v>
       </c>
@@ -4482,20 +4520,20 @@
         <v>258</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>258</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="M62" s="5"/>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>43</v>
       </c>
@@ -4506,20 +4544,20 @@
         <v>258</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>258</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="M63" s="5"/>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>58</v>
       </c>
@@ -4529,21 +4567,21 @@
       <c r="C64" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E64" s="62" t="s">
-        <v>381</v>
-      </c>
-      <c r="F64" s="63" t="s">
-        <v>393</v>
-      </c>
-      <c r="G64" s="61" t="s">
-        <v>384</v>
-      </c>
-      <c r="H64" s="24" t="s">
-        <v>382</v>
+      <c r="E64" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F64" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>305</v>
       </c>
@@ -4553,46 +4591,50 @@
       <c r="C65" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="75" t="s">
+        <v>381</v>
+      </c>
+      <c r="F65" s="63" t="s">
+        <v>393</v>
+      </c>
+      <c r="G65" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="H65" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="M65" s="5"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B66" s="52" t="s">
+        <v>422</v>
+      </c>
+      <c r="C66" s="76" t="s">
+        <v>258</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F65" s="27" t="s">
+      <c r="F66" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="G65" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H65" s="3" t="s">
+      <c r="G66" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="M65" s="5"/>
-    </row>
-    <row r="66" spans="1:13">
-      <c r="E66" s="3" t="s">
+      <c r="M66" s="5"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E67" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F66" s="49" t="s">
+      <c r="F67" s="49" t="s">
         <v>131</v>
-      </c>
-      <c r="G66" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M66" s="5"/>
-    </row>
-    <row r="67" spans="1:13">
-      <c r="A67" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="E67" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F67" s="49" t="s">
-        <v>125</v>
       </c>
       <c r="G67" s="14" t="s">
         <v>258</v>
@@ -4602,23 +4644,19 @@
       </c>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="1:13">
-      <c r="A68" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B68" s="52" t="s">
-        <v>408</v>
-      </c>
-      <c r="C68" s="30" t="s">
-        <v>258</v>
-      </c>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
       <c r="E68" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F68" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="G68" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F68" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="G68" s="14" t="s">
         <v>258</v>
       </c>
       <c r="H68" s="3" t="s">
@@ -4626,23 +4664,23 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B69" s="52" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C69" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E69" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="F69" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="G69" s="14" t="s">
+      <c r="E69" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="G69" s="11" t="s">
         <v>258</v>
       </c>
       <c r="H69" s="3" t="s">
@@ -4650,182 +4688,205 @@
       </c>
       <c r="M69" s="5"/>
     </row>
-    <row r="70" spans="1:13">
-      <c r="E70" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F70" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="H70" s="24" t="s">
-        <v>311</v>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B70" s="52" t="s">
+        <v>409</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="E70" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="F70" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="M70" s="5"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="58" t="s">
+      <c r="E71" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="H71" s="24" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E72" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="F71" s="65" t="s">
+      <c r="F72" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="G71" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H71" s="3" t="s">
+      <c r="G72" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
-      <c r="E72" s="3" t="s">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E73" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F72" s="28" t="s">
+      <c r="F73" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="G72" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H72" s="3" t="s">
+      <c r="G73" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
-      <c r="E73" s="3" t="s">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E74" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F73" s="44" t="s">
+      <c r="F74" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="G73" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="H73" s="24" t="s">
+      <c r="G74" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="H74" s="24" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
-      <c r="E74" s="3" t="s">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E75" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F74" s="28" t="s">
+      <c r="F75" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="G74" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="E75" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="F75" s="40" t="s">
-        <v>323</v>
-      </c>
-      <c r="G75" s="41" t="s">
+      <c r="G75" s="14" t="s">
         <v>258</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E76" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F76" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="G76" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E77" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F76" s="28" t="s">
+      <c r="F77" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="G76" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="H76" s="3" t="s">
+      <c r="G77" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
-      <c r="E77" s="3" t="s">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E78" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F77" s="28" t="s">
+      <c r="F78" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="G77" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="H77" s="3" t="s">
+      <c r="G78" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
-      <c r="E78" s="3" t="s">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E79" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F78" s="28" t="s">
+      <c r="F79" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="G78" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="G79" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
-      <c r="E79" s="3" t="s">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E80" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F79" s="28" t="s">
+      <c r="F80" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="G79" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="H79" s="3" t="s">
+      <c r="G80" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
-      <c r="E80" s="3" t="s">
+    <row r="81" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E81" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="F80" s="43" t="s">
+      <c r="F81" s="43" t="s">
         <v>348</v>
       </c>
-      <c r="G80" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="H80" s="3" t="s">
+      <c r="G81" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="81" spans="5:8">
-      <c r="E81" s="3" t="s">
+    <row r="82" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E82" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F81" s="28" t="s">
+      <c r="F82" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="G81" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="H81" s="3" t="s">
+      <c r="G82" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D15">
-    <sortCondition ref="A3:A15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E4:H82">
+    <sortCondition ref="E82"/>
   </sortState>
-  <phoneticPr fontId="28" type="noConversion"/>
+  <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/模组列表.xlsx
+++ b/模组列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0571EAE6-8732-4940-A13C-7534C01E9F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7FAE7A-35C6-4D97-A416-8D0D04F621CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,10 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="432">
   <si>
     <t>原版名称</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>AetherAspects</t>
@@ -85,1137 +85,1137 @@
   </si>
   <si>
     <t>扩展/优化</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>其他模组</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Achgrate</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>修复模组联动的一些BUG</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>GTNH维护的模组的Lib库</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>1.7.10版本的Mixin总和</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>破坏性修复龙API和魔戒的冲突</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>EntityCulling-Unofficial</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>实体渲染机制优化</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：传承</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>LOTRMod</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">ChromatiCraft </t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Thaumcraft拓展 前置是DragonAPI </t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Middleearththaumaturgy</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>中土神秘学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是LOTRMod</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔戒nei附属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔戒合成</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家, NEI Recipe Handlers</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Aether</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Aether</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Gilded-games-util</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Gilded-games-util</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘生物要素扫描</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>TwilightForest</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>应用能源2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>天境2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>天境要素扫描</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>以太前置库</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>黑暗神秘学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>暮色森林</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>旅者之器</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘基础学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>SpecialMobs</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>特殊怪物</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>LycanitesMobsComplete</t>
   </si>
   <si>
     <t>恐怖生物</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>MoCreatures-Legacy-Final</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>更多生物分支版本</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>WitchingGadgets</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>巫师宝具</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumaturgical Knowledge</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>TravellersGear</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>WarpTheory</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘扭曲学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcarpentry</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘木匠</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘奥义</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThermalFoundation</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>热力基本</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThermalDynamics</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>热动力学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工艺</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>TofuFactoryR</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工厂重制版</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>林业</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>光明之弓</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔法蜜蜂</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Forestry</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是Forestry</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔法曲奇</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>混合魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>MagicalDecorations</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘装饰</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>自然魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>AdvancedThaumaturgy</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>炼金炉篦</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>高等神秘学2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代nei附属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftGates</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>奥法管道</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BC</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>源质罐子统计</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Polybius</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>更多要素</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>TCBotaniaExoflame</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Talismans2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>护身符2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Machina</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘工匠</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicUtilities</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘实用工具</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic_Upholstery</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumores</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>奥能矿物</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicSanity</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>扭曲修正</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicPipes</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘管道</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，MJUtils</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，nei全家</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Additions</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘领域</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ParticleLib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Dyes</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘染料</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘力学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Nexus</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicenergistics</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘能源</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Applied Energistics 2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicalchemy</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘炼金学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicEquivalence</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>奥法置换</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumichorizons</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘视界</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicInfusion</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘注魔</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExpansion</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘膨胀</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExploration</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘探险</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘守望者</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘启示</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔法金属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>量子魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>奥法工程学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ImmersiveEngineering</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneArteries</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>奥法献祭学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Automagy</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>自动化魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Carpenter's Blocks</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Avaritia</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>无尽贪婪</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>血魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>热力核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>CodeChickenCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>鸡块核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>木匠方块</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Carpenter's+Blocks</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>建筑核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>建筑</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是buildcraft-compat</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>植物魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>CraftArcanum</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔改</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ElectricThaum</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>电力魔法工具</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BloodMagic，EvilCraft，Botania</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ImmersiveEngineering</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ElecCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2，ElecCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>EssentialThaumaturgy</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>EssentialCraft3</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>源质神秘学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，EssentialCraft3</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是DummyCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Nihilo</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>无中生有</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Forbidden</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>禁忌魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ForgeMultipart</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Gadomancy</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔像秘经</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Hammerz</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>HeartWork</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>心血结晶</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>InfusionBrewing</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>注魔酿造</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>源质魔法3</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>沉浸工程</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>工业时代2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>IndustrialUpgrade</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>工业升级</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Industrialcraft</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Industrialcraft</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>InventoryTweaks</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>R键整理</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑艺术之刃</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade-SlashArts</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Symcalc</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>对称度运算仪</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>奥数投射</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>等价交换</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Railcraft</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>NodalMechanics</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>节点力学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Technomancy</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Tchelper</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘研究帮助</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Tcinventoryscan</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代物品栏扫描</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Tcnodetracker</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘节点追踪</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Tainted-Magic</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>污秽魔法</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>姆亚核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Shamanry</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>巫媒</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Origin</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ParticleLib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>粒子库</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>铁路</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>DummyCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>齿轮核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，DummyCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>锤子</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>OmnisCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>橘子核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Mjutils</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，PrjectE</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ExtraScepterStaff</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>独角兽权杖</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Boots</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘靴子</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Muya</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Ex-Nihilo</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Localization Optimizer</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代本地化优化</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Not Enough Thaumcraft Tabs</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>无限神秘标签页</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 Tweaks</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>失落遗物学</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Forgotten Relics</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Transmute Liquids</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘标签页</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>液体嬗变</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>星辉生万物重制版</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Astris-Rebirth</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Garden of Glass</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>水晶花园</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置Botania</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>FpsReducer</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Fps减速器</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Thermal热力全家，Origin</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>nei添加更多神秘合成类型显示</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘纠缠</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicBases</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicRevelations</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>AWWayofTime</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔法作物</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>区块预生成器</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>F</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Warden</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicTinkerer</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>IlluminatedBows</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>MagiaNaturalis</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>MagicCookies</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>MixedMagic</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>支持拼音搜索与 JEI 风格的关键字匹配</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneEngineering</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ElectroMagicTools</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>巫术</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Omnis Core，Multipart，CodeChicken Lib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，CodeChicken Lib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>格雷科技6</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>工艺奥秘,电力神秘</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>库</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft联动是TwilightForest,LycanitesMobsComplete,MoCreatures,SpecialMobs</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">  模组重置了NEI的注册系统会在根目录下写入缓存，模组变动一次就会重写一次。会导致加载时间变长很多。放在了可以替换模组的文件夹下。需要使用可以加载。</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>要点</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Aroma1997Core</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>AromaBackup</t>
   </si>
   <si>
     <t>Aroma系列模组核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>备份模组</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Aroma1997Core</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>EnderIO</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>高版本加载界面</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>EnderCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>末影核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>末影接口</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Angelica</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>替代optfine</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>NEI包括附属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Nei合成显示扩展</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>NEI-Integration</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>原版名称</t>
@@ -1231,498 +1231,542 @@
   </si>
   <si>
     <t>前置是Thaumcraft，旧版本译名神秘守望者，还有更古早的叫Thaumic Warden都是这个模组。</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>GregTech 6</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft   Thaumcraft 4 Tweaks类似功能</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Xaeros_Minimap</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Xaero的小地图</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Omnis核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘混成</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicHybrid</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘糅合</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，通过Mixin注入的方式修复了联动和神秘4本身的一些问题</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Integration</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘集合</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftAltarCull</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘祭坛稳定器渲染剔除</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，当玩家远离祭坛时，自动“剔除”稳定器方块 的渲染</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，将Thaumcraft模组的机制和要素整合进其他不原生支持 Thaumcraft 的模组里</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 : Patched</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4：修补</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，NemexLib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>NemexLib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Nemex库</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘温泉</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Renaissance</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘复兴</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是unimixins-all，DragonAPI ，LOTRMod，所有的材质都未实装</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Deathly Hallows</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>死亡圣器</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania，Witchery</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Essentia Pipes</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>管道简化</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Salis Arcana</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>奥秘之盐</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Cybersus</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔能义体</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ItemBlackListFIXED</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>物品黑名单修复版</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>合成冲突消除：修复版</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>RecipeConflict Fixer</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>ChromatiFixes</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：溢出修复</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，修复和其他模组可能导致的工具类数组溢出</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究前置</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>BrandonsCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Draconic-Evolution</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Hell Integrations</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘众戒</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Baubles Expanded和Baubles任选其一</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>前置是Thaumcraft，Avaritia，Botania，Applied Energistics 2，Draconic Evolution，Advanced Solar Panels</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置BrandonsCore</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑西风之刃</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>LOTweakR</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元修复</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元另一个修复</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">前置是ChromatiCraft </t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>安装可否</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Bugtorch</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Gtnhlib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>中文名/注释</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Modernsplash</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Unimixins-all</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft-compat</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Jar Checker</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>地狱合集</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>联动模组</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Trop</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicthermae</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicmixins</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Manametalmod</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Magicbees</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Witchery</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Neiaddons</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Nechar-GTNH（NotEnoughCharacters）</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Tcneiadditions</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Lotrcrashfix</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>NeiRecipeHandlers</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>NeiLotr</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Minus Thaumcraft</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Errata</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，联动了Grimoire of Gaia，Automagy，Thermal Foundation</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑包括附属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是SlashBlade</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade，SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Magicalcrops</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>以太2包括附属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>魔戒包括附属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元以及修复</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrialcraft，Tainted Magic，Electro Magic Tools（EMT）</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>神秘联动 1.1.2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑-暗鸦 1.1.2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>红色名字是作者反编译+修BUG后重新打包的模组。绿色名字是新加的模组后面是整合包版本号</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Chromaticraft-AIFixes（Zaifix）</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>JAOPC</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>另一版本的统一矿物</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>CarbonConfig</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator的核心</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是CarbonConfig</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>自动解锁所有神秘时代研究1.2.2</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>chunkapi</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>endlessids</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>我看到了什么</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>wdmla</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>Wawla</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>waila的fork版本</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>拓展所有ID</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>falsepatternlib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是chunkapi，falsepatternlib</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>对非 libraries 模组进行版本安全的依赖处理</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>将自定义数据添加到区块的模组</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>forgelin-GTNH</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，forgelin-GTNH</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
     <t>ThaumcraftResearchTweaks</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>研究工具 1.1.6</t>
-    <phoneticPr fontId="29" type="noConversion"/>
-  </si>
-  <si>
-    <t>forgelin</t>
-    <phoneticPr fontId="29" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>WailaHarvestability</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Waila Plugins</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1.6.2版本后被移除</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>waila的附属，工具条件</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>waila的附属，更多显示</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>MouseTweaks</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼠标手势</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>forgelin库</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>journeymap</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>旅行地图</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置是Thaumcraft，Avaritia，Botania，Applied Energistics 2，Draconic Evolution，Advanced Solar Panels移除</t>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2016,6 +2060,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2084,252 +2143,276 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2640,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>282</v>
@@ -2655,7 +2738,7 @@
         <v>299</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>301</v>
@@ -2681,14 +2764,14 @@
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -2703,7 +2786,7 @@
         <v>294</v>
       </c>
       <c r="C3" s="74" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
@@ -2806,7 +2889,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>17</v>
@@ -2827,7 +2910,7 @@
         <v>162</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J6" s="26" t="s">
         <v>260</v>
@@ -2841,10 +2924,10 @@
     </row>
     <row r="7" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>399</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>400</v>
       </c>
       <c r="C7" s="67" t="s">
         <v>258</v>
@@ -2862,7 +2945,7 @@
         <v>163</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J7" s="28" t="s">
         <v>76</v>
@@ -2886,7 +2969,7 @@
         <v>258</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>141</v>
@@ -2901,7 +2984,7 @@
         <v>27</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J8" s="28" t="s">
         <v>135</v>
@@ -2988,7 +3071,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>18</v>
@@ -3024,7 +3107,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>21</v>
@@ -3048,7 +3131,7 @@
         <v>166</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>272</v>
@@ -3063,7 +3146,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>289</v>
@@ -3087,10 +3170,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C14" s="71" t="s">
         <v>258</v>
@@ -3108,7 +3191,7 @@
         <v>27</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -3117,7 +3200,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B15" s="68" t="s">
         <v>19</v>
@@ -3151,10 +3234,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B16" s="73" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C16" s="71" t="s">
         <v>258</v>
@@ -3172,7 +3255,7 @@
         <v>27</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J16" s="28" t="s">
         <v>36</v>
@@ -3187,16 +3270,16 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C17" s="71" t="s">
         <v>258</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>175</v>
@@ -3211,7 +3294,7 @@
         <v>27</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J17" s="28" t="s">
         <v>35</v>
@@ -3264,7 +3347,7 @@
         <v>27</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J19" s="28" t="s">
         <v>341</v>
@@ -3279,26 +3362,26 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B20" s="66" t="s">
-        <v>398</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20"/>
-      <c r="E20" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B20" s="85" t="s">
+        <v>306</v>
+      </c>
+      <c r="C20" s="81"/>
+      <c r="D20" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E20" s="80" t="s">
         <v>347</v>
       </c>
-      <c r="F20" s="48" t="s">
-        <v>366</v>
-      </c>
-      <c r="G20" s="42" t="s">
-        <v>258</v>
+      <c r="F20" s="83" t="s">
+        <v>365</v>
+      </c>
+      <c r="G20" s="84" t="s">
+        <v>262</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -3310,11 +3393,14 @@
       <c r="A21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>258</v>
+      <c r="B21" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>265</v>
@@ -3329,7 +3415,7 @@
         <v>27</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -3340,11 +3426,14 @@
       <c r="A22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>258</v>
+      <c r="B22" s="51" t="s">
+        <v>343</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>183</v>
@@ -3374,11 +3463,14 @@
       <c r="A23" s="57" t="s">
         <v>259</v>
       </c>
-      <c r="B23" s="39" t="s">
-        <v>146</v>
+      <c r="B23" s="27" t="s">
+        <v>153</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>258</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>266</v>
@@ -3410,11 +3502,14 @@
       <c r="A24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>258</v>
+      <c r="B24" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>81</v>
@@ -3446,11 +3541,14 @@
       <c r="A25" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B25" s="51" t="s">
-        <v>344</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>258</v>
+      <c r="B25" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>267</v>
@@ -3468,16 +3566,16 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="C26" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>258</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>154</v>
+        <v>409</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>268</v>
@@ -3501,14 +3599,15 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B27" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>258</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="B27" s="66" t="s">
+        <v>397</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="D27"/>
       <c r="E27" s="3" t="s">
         <v>204</v>
       </c>
@@ -3522,7 +3621,7 @@
         <v>27</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J27" s="25" t="s">
         <v>254</v>
@@ -3531,7 +3630,7 @@
         <v>258</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M27" s="5"/>
     </row>
@@ -3540,9 +3639,9 @@
         <v>151</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>258</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -3558,7 +3657,7 @@
         <v>304</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J28" s="26" t="s">
         <v>269</v>
@@ -3567,7 +3666,7 @@
         <v>258</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M28" s="5"/>
     </row>
@@ -3575,10 +3674,10 @@
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="C29" s="30" t="s">
+      <c r="B29" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>258</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -3594,7 +3693,7 @@
         <v>27</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J29" s="26" t="s">
         <v>296</v>
@@ -3603,7 +3702,7 @@
         <v>258</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M29" s="5"/>
     </row>
@@ -3611,10 +3710,10 @@
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30" s="30" t="s">
+      <c r="B30" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>258</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -3639,7 +3738,7 @@
         <v>258</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M30" s="5"/>
     </row>
@@ -3647,10 +3746,10 @@
       <c r="A31" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="C31" s="31" t="s">
+      <c r="B31" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>258</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -3672,13 +3771,10 @@
         <v>346</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C32" s="45" t="s">
         <v>258</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>198</v>
@@ -3693,7 +3789,7 @@
         <v>27</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
@@ -3704,10 +3800,10 @@
       <c r="A33" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="C33" s="30" t="s">
+      <c r="B33" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>258</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -3740,10 +3836,10 @@
       <c r="A34" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="C34" s="32" t="s">
+      <c r="B34" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>258</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -3762,13 +3858,13 @@
         <v>340</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K34" s="47" t="s">
         <v>258</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M34" s="5"/>
     </row>
@@ -3777,9 +3873,9 @@
         <v>290</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="C35" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -3795,16 +3891,16 @@
         <v>201</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J35" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="K35" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="K35" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="M35" s="5"/>
     </row>
@@ -3813,9 +3909,9 @@
         <v>288</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="C36" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -3837,13 +3933,10 @@
         <v>168</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>258</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>209</v>
@@ -3858,7 +3951,7 @@
         <v>27</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
@@ -3870,7 +3963,7 @@
         <v>173</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>258</v>
@@ -3902,9 +3995,9 @@
         <v>77</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="32" t="s">
         <v>258</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -3920,16 +4013,16 @@
         <v>27</v>
       </c>
       <c r="I39" s="62" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J39" s="64" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K39" s="32" t="s">
         <v>258</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M39" s="5"/>
     </row>
@@ -3938,9 +4031,9 @@
         <v>177</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="C40" s="36" t="s">
         <v>258</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -3959,7 +4052,7 @@
         <v>9</v>
       </c>
       <c r="J40" s="50" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K40" s="19" t="s">
         <v>258</v>
@@ -3974,13 +4067,10 @@
         <v>248</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>250</v>
+        <v>292</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>258</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>64</v>
@@ -4013,7 +4103,7 @@
         <v>138</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C42" s="30" t="s">
         <v>258</v>
@@ -4040,7 +4130,7 @@
         <v>258</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M42" s="5"/>
     </row>
@@ -4049,7 +4139,7 @@
         <v>190</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="C43" s="30" t="s">
         <v>258</v>
@@ -4073,7 +4163,7 @@
         <v>188</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="C44" s="30" t="s">
         <v>258</v>
@@ -4097,16 +4187,13 @@
         <v>192</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C45" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="E45" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F45" s="48" t="s">
         <v>91</v>
@@ -4123,10 +4210,10 @@
       <c r="A46" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B46" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="C46" s="45" t="s">
+      <c r="B46" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C46" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -4151,16 +4238,16 @@
         <v>54</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>55</v>
+        <v>189</v>
       </c>
       <c r="C47" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E47" s="75" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F47" s="70" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G47" s="69" t="s">
         <v>262</v>
@@ -4174,10 +4261,10 @@
       <c r="A48" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B48" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="C48" s="30" t="s">
+      <c r="B48" s="51" t="s">
+        <v>337</v>
+      </c>
+      <c r="C48" s="45" t="s">
         <v>258</v>
       </c>
       <c r="E48" s="3" t="s">
@@ -4199,7 +4286,7 @@
         <v>56</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C49" s="30" t="s">
         <v>258</v>
@@ -4223,9 +4310,9 @@
         <v>6</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="C50" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="C50" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E50" s="3" t="s">
@@ -4247,7 +4334,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="C51" s="30" t="s">
         <v>258</v>
@@ -4270,23 +4357,23 @@
       <c r="A52" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B52" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="C52" s="36" t="s">
+      <c r="B52" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" s="31" t="s">
         <v>258</v>
       </c>
       <c r="E52" s="75" t="s">
+        <v>419</v>
+      </c>
+      <c r="F52" s="77" t="s">
         <v>420</v>
       </c>
-      <c r="F52" s="77" t="s">
-        <v>421</v>
-      </c>
       <c r="G52" s="16" t="s">
         <v>258</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M52" s="5"/>
     </row>
@@ -4294,14 +4381,11 @@
       <c r="A53" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B53" s="33" t="s">
-        <v>307</v>
+      <c r="B53" s="29" t="s">
+        <v>215</v>
       </c>
       <c r="C53" s="30" t="s">
         <v>258</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>110</v>
@@ -4321,10 +4405,10 @@
       <c r="A54" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B54" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="C54" s="30" t="s">
+      <c r="B54" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="C54" s="36" t="s">
         <v>258</v>
       </c>
       <c r="E54" s="3" t="s">
@@ -4337,7 +4421,7 @@
         <v>258</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M54" s="5"/>
     </row>
@@ -4346,9 +4430,9 @@
         <v>219</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="C55" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C55" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -4370,9 +4454,9 @@
         <v>8</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="C56" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="C56" s="34" t="s">
         <v>258</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -4393,10 +4477,10 @@
       <c r="A57" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B57" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="C57" s="45" t="s">
+      <c r="B57" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E57" s="3" t="s">
@@ -4417,10 +4501,10 @@
       <c r="A58" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="30" t="s">
+      <c r="B58" s="86" t="s">
+        <v>338</v>
+      </c>
+      <c r="C58" s="45" t="s">
         <v>258</v>
       </c>
       <c r="E58" s="3" t="s">
@@ -4442,7 +4526,7 @@
         <v>69</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C59" s="30" t="s">
         <v>258</v>
@@ -4466,7 +4550,7 @@
         <v>67</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C60" s="30" t="s">
         <v>258</v>
@@ -4490,7 +4574,7 @@
         <v>72</v>
       </c>
       <c r="B61" s="53" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C61" s="30" t="s">
         <v>258</v>
@@ -4514,7 +4598,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C62" s="30" t="s">
         <v>258</v>
@@ -4538,7 +4622,7 @@
         <v>43</v>
       </c>
       <c r="B63" s="53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C63" s="30" t="s">
         <v>258</v>
@@ -4562,7 +4646,7 @@
         <v>58</v>
       </c>
       <c r="B64" s="53" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C64" s="30" t="s">
         <v>258</v>
@@ -4582,35 +4666,35 @@
       <c r="M64" s="5"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="80" t="s">
         <v>305</v>
       </c>
-      <c r="B65" s="52" t="s">
-        <v>306</v>
+      <c r="B65" s="53" t="s">
+        <v>59</v>
       </c>
       <c r="C65" s="30" t="s">
         <v>258</v>
       </c>
       <c r="E65" s="75" t="s">
+        <v>380</v>
+      </c>
+      <c r="F65" s="63" t="s">
+        <v>392</v>
+      </c>
+      <c r="G65" s="61" t="s">
+        <v>383</v>
+      </c>
+      <c r="H65" s="24" t="s">
         <v>381</v>
-      </c>
-      <c r="F65" s="63" t="s">
-        <v>393</v>
-      </c>
-      <c r="G65" s="61" t="s">
-        <v>384</v>
-      </c>
-      <c r="H65" s="24" t="s">
-        <v>382</v>
       </c>
       <c r="M65" s="5"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B66" s="52" t="s">
-        <v>422</v>
+        <v>416</v>
+      </c>
+      <c r="B66" s="79" t="s">
+        <v>428</v>
       </c>
       <c r="C66" s="76" t="s">
         <v>258</v>
@@ -4630,6 +4714,15 @@
       <c r="M66" s="5"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B67" s="79" t="s">
+        <v>427</v>
+      </c>
+      <c r="C67" s="82" t="s">
+        <v>258</v>
+      </c>
       <c r="E67" s="3" t="s">
         <v>130</v>
       </c>
@@ -4645,11 +4738,15 @@
       <c r="M67" s="5"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
+      <c r="A68" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B68" s="79" t="s">
+        <v>430</v>
+      </c>
+      <c r="C68" s="82" t="s">
+        <v>258</v>
+      </c>
       <c r="E68" s="3" t="s">
         <v>124</v>
       </c>
@@ -4665,15 +4762,6 @@
       <c r="M68" s="5"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B69" s="52" t="s">
-        <v>408</v>
-      </c>
-      <c r="C69" s="30" t="s">
-        <v>258</v>
-      </c>
       <c r="E69" s="3" t="s">
         <v>309</v>
       </c>
@@ -4689,15 +4777,11 @@
       <c r="M69" s="5"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B70" s="52" t="s">
-        <v>409</v>
-      </c>
-      <c r="C70" s="30" t="s">
-        <v>258</v>
-      </c>
+      <c r="A70" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
       <c r="E70" s="58" t="s">
         <v>126</v>
       </c>
@@ -4713,10 +4797,18 @@
       <c r="M70" s="5"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
+      <c r="A71" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B71" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>258</v>
+      </c>
       <c r="D71" s="5"/>
       <c r="E71" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F71" s="28" t="s">
         <v>310</v>
@@ -4729,6 +4821,15 @@
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B72" s="79" t="s">
+        <v>408</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>258</v>
+      </c>
       <c r="E72" s="58" t="s">
         <v>116</v>
       </c>
@@ -4743,6 +4844,15 @@
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B73" s="79" t="s">
+        <v>425</v>
+      </c>
+      <c r="C73" s="82" t="s">
+        <v>258</v>
+      </c>
       <c r="E73" s="3" t="s">
         <v>106</v>
       </c>
@@ -4757,6 +4867,15 @@
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B74" s="79" t="s">
+        <v>424</v>
+      </c>
+      <c r="C74" s="82" t="s">
+        <v>258</v>
+      </c>
       <c r="E74" s="3" t="s">
         <v>257</v>
       </c>
@@ -4786,7 +4905,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E76" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F76" s="40" t="s">
         <v>323</v>
@@ -4856,7 +4975,7 @@
     </row>
     <row r="81" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E81" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F81" s="43" t="s">
         <v>348</v>
@@ -4883,10 +5002,10 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E4:H82">
-    <sortCondition ref="E82"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B20:D68">
+    <sortCondition ref="D68"/>
   </sortState>
-  <phoneticPr fontId="29" type="noConversion"/>
+  <phoneticPr fontId="30" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/模组列表.xlsx
+++ b/模组列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7FAE7A-35C6-4D97-A416-8D0D04F621CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555BFB10-6B27-4A61-A009-4A0F2FE45E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,10 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="434">
   <si>
     <t>原版名称</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>AetherAspects</t>
@@ -85,1137 +85,1125 @@
   </si>
   <si>
     <t>扩展/优化</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>其他模组</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Achgrate</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>修复模组联动的一些BUG</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>GTNH维护的模组的Lib库</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>1.7.10版本的Mixin总和</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>破坏性修复龙API和魔戒的冲突</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>EntityCulling-Unofficial</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>实体渲染机制优化</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：传承</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>LOTRMod</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">ChromatiCraft </t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Thaumcraft拓展 前置是DragonAPI </t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Middleearththaumaturgy</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>中土神秘学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是LOTRMod</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔戒nei附属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔戒合成</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家, NEI Recipe Handlers</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Aether</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Aether</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Gilded-games-util</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Gilded-games-util</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘生物要素扫描</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>TwilightForest</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>应用能源2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>天境2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>天境要素扫描</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>以太前置库</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>黑暗神秘学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>暮色森林</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>旅者之器</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘基础学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>SpecialMobs</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>特殊怪物</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>LycanitesMobsComplete</t>
   </si>
   <si>
     <t>恐怖生物</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>MoCreatures-Legacy-Final</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>更多生物分支版本</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>WitchingGadgets</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>巫师宝具</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumaturgical Knowledge</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>TravellersGear</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>WarpTheory</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘扭曲学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcarpentry</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘木匠</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘奥义</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThermalFoundation</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>热力基本</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThermalDynamics</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>热动力学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工艺</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>TofuFactoryR</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工厂重制版</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>林业</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>光明之弓</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔法蜜蜂</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Forestry</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是Forestry</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔法曲奇</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>混合魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>MagicalDecorations</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘装饰</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>自然魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>AdvancedThaumaturgy</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>炼金炉篦</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>高等神秘学2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代nei附属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftGates</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>奥法管道</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BC</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>源质罐子统计</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Polybius</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>更多要素</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>TCBotaniaExoflame</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Talismans2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>护身符2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Machina</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘工匠</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicUtilities</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘实用工具</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic_Upholstery</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumores</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>奥能矿物</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicSanity</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>扭曲修正</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicPipes</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘管道</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，MJUtils</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，nei全家</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Additions</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘领域</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ParticleLib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Dyes</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘染料</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘力学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Nexus</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicenergistics</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘能源</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Applied Energistics 2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicalchemy</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘炼金学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicEquivalence</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>奥法置换</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumichorizons</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘视界</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicInfusion</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘注魔</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExpansion</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘膨胀</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExploration</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘探险</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘守望者</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘启示</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔法金属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>量子魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>奥法工程学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ImmersiveEngineering</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneArteries</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>奥法献祭学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Automagy</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>自动化魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Carpenter's Blocks</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Avaritia</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>无尽贪婪</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>血魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>热力核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>CodeChickenCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>鸡块核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>木匠方块</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Carpenter's+Blocks</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>建筑核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>建筑</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是buildcraft-compat</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>植物魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>CraftArcanum</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔改</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ElectricThaum</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>电力魔法工具</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BloodMagic，EvilCraft，Botania</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ImmersiveEngineering</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ElecCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2，ElecCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>EssentialThaumaturgy</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>EssentialCraft3</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>源质神秘学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，EssentialCraft3</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是DummyCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Nihilo</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>无中生有</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Forbidden</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>禁忌魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ForgeMultipart</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Gadomancy</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔像秘经</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Hammerz</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>HeartWork</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>心血结晶</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>InfusionBrewing</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>注魔酿造</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>源质魔法3</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>沉浸工程</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>工业时代2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>IndustrialUpgrade</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>工业升级</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Industrialcraft</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Industrialcraft</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>InventoryTweaks</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>R键整理</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑艺术之刃</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade-SlashArts</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Symcalc</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>对称度运算仪</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>奥数投射</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>等价交换</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Railcraft</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>NodalMechanics</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>节点力学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Technomancy</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Tchelper</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘研究帮助</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Tcinventoryscan</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代物品栏扫描</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Tcnodetracker</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘节点追踪</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Tainted-Magic</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>污秽魔法</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>姆亚核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Shamanry</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>巫媒</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Origin</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ParticleLib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>粒子库</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>铁路</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>DummyCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>齿轮核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，DummyCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>锤子</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>OmnisCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>橘子核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Mjutils</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，PrjectE</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ExtraScepterStaff</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>独角兽权杖</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Boots</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘靴子</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Muya</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Ex-Nihilo</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Localization Optimizer</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代本地化优化</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Not Enough Thaumcraft Tabs</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>无限神秘标签页</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 Tweaks</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>失落遗物学</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Forgotten Relics</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Transmute Liquids</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘标签页</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>液体嬗变</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>星辉生万物重制版</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Astris-Rebirth</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Garden of Glass</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>水晶花园</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置Botania</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>FpsReducer</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Fps减速器</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Thermal热力全家，Origin</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>nei添加更多神秘合成类型显示</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘纠缠</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicBases</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicRevelations</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>AWWayofTime</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔法作物</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>区块预生成器</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>F</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Warden</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicTinkerer</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>IlluminatedBows</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>MagiaNaturalis</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>MagicCookies</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>MixedMagic</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>支持拼音搜索与 JEI 风格的关键字匹配</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneEngineering</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ElectroMagicTools</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>巫术</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Omnis Core，Multipart，CodeChicken Lib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，CodeChicken Lib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>格雷科技6</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>工艺奥秘,电力神秘</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>库</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft联动是TwilightForest,LycanitesMobsComplete,MoCreatures,SpecialMobs</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">  模组重置了NEI的注册系统会在根目录下写入缓存，模组变动一次就会重写一次。会导致加载时间变长很多。放在了可以替换模组的文件夹下。需要使用可以加载。</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>要点</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Aroma1997Core</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>AromaBackup</t>
   </si>
   <si>
     <t>Aroma系列模组核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>备份模组</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Aroma1997Core</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>EnderIO</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>高版本加载界面</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>EnderCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>末影核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>末影接口</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Angelica</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>替代optfine</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>NEI包括附属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Nei合成显示扩展</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>NEI-Integration</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>原版名称</t>
@@ -1231,534 +1219,570 @@
   </si>
   <si>
     <t>前置是Thaumcraft，旧版本译名神秘守望者，还有更古早的叫Thaumic Warden都是这个模组。</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>GregTech 6</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft   Thaumcraft 4 Tweaks类似功能</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Xaeros_Minimap</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Xaero的小地图</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Omnis核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘混成</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicHybrid</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘糅合</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，通过Mixin注入的方式修复了联动和神秘4本身的一些问题</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Integration</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘集合</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftAltarCull</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘祭坛稳定器渲染剔除</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，当玩家远离祭坛时，自动“剔除”稳定器方块 的渲染</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，将Thaumcraft模组的机制和要素整合进其他不原生支持 Thaumcraft 的模组里</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 : Patched</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4：修补</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，NemexLib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>NemexLib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Nemex库</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘温泉</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Renaissance</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘复兴</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是unimixins-all，DragonAPI ，LOTRMod，所有的材质都未实装</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Deathly Hallows</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>死亡圣器</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania，Witchery</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Essentia Pipes</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>管道简化</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Salis Arcana</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>奥秘之盐</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Cybersus</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔能义体</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ItemBlackListFIXED</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>物品黑名单修复版</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>合成冲突消除：修复版</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>RecipeConflict Fixer</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>ChromatiFixes</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：溢出修复</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，修复和其他模组可能导致的工具类数组溢出</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究前置</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>BrandonsCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Draconic-Evolution</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Hell Integrations</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘众戒</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Baubles Expanded和Baubles任选其一</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置BrandonsCore</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑西风之刃</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>LOTweakR</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元修复</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元另一个修复</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">前置是ChromatiCraft </t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>安装可否</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Bugtorch</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Gtnhlib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>中文名/注释</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Modernsplash</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Unimixins-all</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft-compat</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Jar Checker</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>地狱合集</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>联动模组</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Trop</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicthermae</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicmixins</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Manametalmod</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Magicbees</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Witchery</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Neiaddons</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Nechar-GTNH（NotEnoughCharacters）</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Tcneiadditions</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Lotrcrashfix</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>NeiRecipeHandlers</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>NeiLotr</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Minus Thaumcraft</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Errata</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，联动了Grimoire of Gaia，Automagy，Thermal Foundation</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑包括附属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是SlashBlade</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade，SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Magicalcrops</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>以太2包括附属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>魔戒包括附属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元以及修复</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrialcraft，Tainted Magic，Electro Magic Tools（EMT）</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>神秘联动 1.1.2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑-暗鸦 1.1.2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>红色名字是作者反编译+修BUG后重新打包的模组。绿色名字是新加的模组后面是整合包版本号</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Chromaticraft-AIFixes（Zaifix）</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>JAOPC</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>另一版本的统一矿物</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>CarbonConfig</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator的核心</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是CarbonConfig</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>自动解锁所有神秘时代研究1.2.2</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>chunkapi</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>endlessids</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>我看到了什么</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>wdmla</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Wawla</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>waila的fork版本</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>拓展所有ID</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>falsepatternlib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是chunkapi，falsepatternlib</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>对非 libraries 模组进行版本安全的依赖处理</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>将自定义数据添加到区块的模组</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>forgelin-GTNH</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，forgelin-GTNH</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
     <t>ThaumcraftResearchTweaks</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>研究工具 1.1.6</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>WailaHarvestability</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>Waila Plugins</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>1.1.6.2版本后被移除</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属，工具条件</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属，更多显示</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>MouseTweaks</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>鼠标手势</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>forgelin库</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>journeymap</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>旅行地图</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Avaritia，Botania，Applied Energistics 2，Draconic Evolution，Advanced Solar Panels移除</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>源质魔法4</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>EssentialCraft4</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>ForgeMultipart库</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mjutils库</t>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="43" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2143,275 +2167,281 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2723,37 +2753,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>301</v>
-      </c>
       <c r="I1" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="L1" s="24" t="s">
         <v>298</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>301</v>
       </c>
       <c r="M1" s="5"/>
     </row>
@@ -2764,14 +2794,14 @@
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -2780,13 +2810,13 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C3" s="74" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
@@ -2795,32 +2825,32 @@
         <v>20</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>16</v>
@@ -2829,19 +2859,19 @@
         <v>85</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>132</v>
@@ -2850,16 +2880,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>84</v>
@@ -2868,19 +2898,19 @@
         <v>86</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>132</v>
@@ -2889,13 +2919,13 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E6" s="59" t="s">
         <v>139</v>
@@ -2904,19 +2934,19 @@
         <v>140</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>162</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>132</v>
@@ -2924,34 +2954,34 @@
     </row>
     <row r="7" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F7" s="49" t="s">
         <v>137</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>163</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J7" s="28" t="s">
         <v>76</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>78</v>
@@ -2963,13 +2993,13 @@
         <v>156</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>141</v>
@@ -2978,22 +3008,22 @@
         <v>142</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J8" s="28" t="s">
         <v>135</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="M8" s="5"/>
     </row>
@@ -3005,16 +3035,16 @@
         <v>23</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>157</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>163</v>
@@ -3026,7 +3056,7 @@
         <v>32</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>33</v>
@@ -3035,34 +3065,34 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>132</v>
@@ -3071,25 +3101,25 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
@@ -3098,7 +3128,7 @@
         <v>71</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>132</v>
@@ -3107,16 +3137,16 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>159</v>
@@ -3125,19 +3155,19 @@
         <v>161</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>166</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>132</v>
@@ -3146,22 +3176,22 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>160</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>164</v>
@@ -3170,28 +3200,28 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C14" s="71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G14" s="42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -3200,25 +3230,25 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B15" s="68" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>167</v>
       </c>
       <c r="F15" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>25</v>
@@ -3227,41 +3257,41 @@
         <v>24</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B16" s="73" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J16" s="28" t="s">
         <v>36</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>34</v>
@@ -3270,37 +3300,37 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C17" s="71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>176</v>
-      </c>
       <c r="G17" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>37</v>
@@ -3309,19 +3339,19 @@
     </row>
     <row r="18" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I18" s="56" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J18" s="56"/>
       <c r="K18" s="56"/>
@@ -3335,53 +3365,52 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="E19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="F19" s="28" t="s">
-        <v>179</v>
-      </c>
       <c r="G19" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="B20" s="85" t="s">
-        <v>306</v>
-      </c>
-      <c r="C20" s="81"/>
-      <c r="D20" s="3" t="s">
-        <v>423</v>
+        <v>393</v>
+      </c>
+      <c r="B20" s="66" t="s">
+        <v>394</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>256</v>
       </c>
       <c r="E20" s="80" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F20" s="83" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G20" s="84" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -3393,29 +3422,26 @@
       <c r="A21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="29" t="s">
-        <v>249</v>
+      <c r="B21" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F21" s="49" t="s">
         <v>75</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -3426,23 +3452,20 @@
       <c r="A22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="51" t="s">
-        <v>343</v>
+      <c r="B22" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F22" s="49" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="49" t="s">
-        <v>184</v>
-      </c>
       <c r="G22" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>27</v>
@@ -3454,32 +3477,29 @@
         <v>47</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>153</v>
+        <v>257</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>146</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F23" s="49" t="s">
         <v>83</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>27</v>
@@ -3491,7 +3511,7 @@
         <v>45</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>41</v>
@@ -3502,14 +3522,11 @@
       <c r="A24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="29" t="s">
-        <v>185</v>
+      <c r="B24" s="27" t="s">
+        <v>155</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>81</v>
@@ -3518,7 +3535,7 @@
         <v>82</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>27</v>
@@ -3530,7 +3547,7 @@
         <v>46</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>39</v>
@@ -3539,25 +3556,25 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>193</v>
+        <v>342</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>341</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>191</v>
+        <v>406</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>79</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>27</v>
@@ -3566,31 +3583,31 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>307</v>
+        <v>359</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>153</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>409</v>
+        <v>154</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F26" s="28" t="s">
         <v>80</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
@@ -3599,38 +3616,38 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B27" s="66" t="s">
-        <v>397</v>
+        <v>360</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>152</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D27"/>
       <c r="E27" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M27" s="5"/>
     </row>
@@ -3639,34 +3656,34 @@
         <v>151</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J28" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M28" s="5"/>
     </row>
@@ -3674,11 +3691,11 @@
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="27" t="s">
-        <v>145</v>
+      <c r="B29" s="29" t="s">
+        <v>149</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>92</v>
@@ -3687,22 +3704,22 @@
         <v>93</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J29" s="26" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M29" s="5"/>
     </row>
@@ -3710,35 +3727,35 @@
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="39" t="s">
-        <v>146</v>
+      <c r="B30" s="29" t="s">
+        <v>147</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F30" s="43" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="J30" s="26" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="M30" s="5"/>
     </row>
@@ -3746,20 +3763,20 @@
       <c r="A31" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="27" t="s">
-        <v>155</v>
+      <c r="B31" s="29" t="s">
+        <v>158</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>27</v>
@@ -3768,28 +3785,31 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>258</v>
+        <v>256</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
@@ -3798,22 +3818,22 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>152</v>
+        <v>220</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>221</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>27</v>
@@ -3825,7 +3845,7 @@
         <v>29</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>30</v>
@@ -3836,11 +3856,11 @@
       <c r="A34" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="27" t="s">
-        <v>150</v>
+      <c r="B34" s="29" t="s">
+        <v>171</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>95</v>
@@ -3849,79 +3869,79 @@
         <v>96</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="K34" s="47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M34" s="5"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>149</v>
+        <v>288</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J35" s="46" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="K35" s="47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M35" s="5"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>147</v>
+        <v>289</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>27</v>
@@ -3930,28 +3950,31 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>158</v>
+        <v>430</v>
+      </c>
+      <c r="B37" s="87" t="s">
+        <v>429</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>258</v>
+        <v>256</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
@@ -3960,34 +3983,34 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="B38" s="29" t="s">
-        <v>223</v>
-      </c>
       <c r="C38" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J38" s="29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K38" s="32" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -3995,46 +4018,46 @@
         <v>77</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F39" s="28" t="s">
         <v>136</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I39" s="62" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J39" s="64" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K39" s="32" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="M39" s="5"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B40" s="29" t="s">
-        <v>291</v>
+        <v>176</v>
+      </c>
+      <c r="B40" s="88" t="s">
+        <v>432</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>60</v>
@@ -4043,7 +4066,7 @@
         <v>66</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>27</v>
@@ -4052,25 +4075,28 @@
         <v>9</v>
       </c>
       <c r="J40" s="50" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="M40" s="5"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="B41" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="C41" s="36" t="s">
-        <v>258</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>64</v>
@@ -4079,22 +4105,22 @@
         <v>65</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>143</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J41" s="49" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K41" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="M41" s="5"/>
     </row>
@@ -4103,55 +4129,55 @@
         <v>138</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G42" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I42" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="J42" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="J42" s="28" t="s">
-        <v>182</v>
-      </c>
       <c r="K42" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="M42" s="5"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F43" s="49" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>27</v>
@@ -4160,46 +4186,49 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>277</v>
+        <v>187</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G44" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M44" s="5"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E45" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F45" s="48" t="s">
         <v>91</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>27</v>
@@ -4208,28 +4237,28 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B46" s="29" t="s">
-        <v>187</v>
+        <v>333</v>
+      </c>
+      <c r="B46" s="51" t="s">
+        <v>334</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M46" s="5"/>
     </row>
@@ -4238,19 +4267,19 @@
         <v>54</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E47" s="75" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F47" s="70" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G47" s="69" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>27</v>
@@ -4259,25 +4288,25 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B48" s="51" t="s">
-        <v>337</v>
+        <v>226</v>
+      </c>
+      <c r="B48" s="88" t="s">
+        <v>433</v>
       </c>
       <c r="C48" s="45" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G48" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M48" s="5"/>
     </row>
@@ -4286,10 +4315,10 @@
         <v>56</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E49" t="s">
         <v>88</v>
@@ -4298,7 +4327,7 @@
         <v>89</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>90</v>
@@ -4310,10 +4339,10 @@
         <v>6</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>277</v>
+        <v>158</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>10</v>
@@ -4322,10 +4351,10 @@
         <v>42</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H50" s="55" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M50" s="5"/>
     </row>
@@ -4334,10 +4363,10 @@
         <v>7</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>57</v>
+        <v>213</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>11</v>
@@ -4346,7 +4375,7 @@
         <v>87</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>109</v>
@@ -4355,37 +4384,37 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B52" s="29" t="s">
-        <v>158</v>
+        <v>318</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>319</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E52" s="75" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F52" s="77" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="M52" s="5"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B53" s="29" t="s">
-        <v>215</v>
+        <v>224</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>304</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>110</v>
@@ -4394,7 +4423,7 @@
         <v>111</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>112</v>
@@ -4403,37 +4432,37 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B54" s="51" t="s">
-        <v>322</v>
+        <v>216</v>
+      </c>
+      <c r="B54" s="29" t="s">
+        <v>225</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="M54" s="5"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>97</v>
@@ -4442,7 +4471,7 @@
         <v>115</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>27</v>
@@ -4454,19 +4483,19 @@
         <v>8</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F56" s="44" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G56" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>27</v>
@@ -4475,22 +4504,22 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B57" s="29" t="s">
-        <v>202</v>
+        <v>336</v>
+      </c>
+      <c r="B57" s="86" t="s">
+        <v>335</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F57" s="49" t="s">
         <v>133</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>27</v>
@@ -4501,11 +4530,11 @@
       <c r="A58" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="86" t="s">
-        <v>338</v>
+      <c r="B58" s="53" t="s">
+        <v>53</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>101</v>
@@ -4514,7 +4543,7 @@
         <v>82</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>27</v>
@@ -4526,10 +4555,10 @@
         <v>69</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E59" s="59" t="s">
         <v>120</v>
@@ -4538,7 +4567,7 @@
         <v>121</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>27</v>
@@ -4550,22 +4579,22 @@
         <v>67</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E60" s="58" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F60" s="78" t="s">
         <v>51</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M60" s="5"/>
     </row>
@@ -4574,10 +4603,10 @@
         <v>72</v>
       </c>
       <c r="B61" s="53" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E61" s="58" t="s">
         <v>12</v>
@@ -4586,7 +4615,7 @@
         <v>48</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>27</v>
@@ -4598,10 +4627,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>113</v>
@@ -4610,7 +4639,7 @@
         <v>114</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>27</v>
@@ -4622,10 +4651,10 @@
         <v>43</v>
       </c>
       <c r="B63" s="53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>117</v>
@@ -4634,7 +4663,7 @@
         <v>118</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>119</v>
@@ -4646,10 +4675,10 @@
         <v>58</v>
       </c>
       <c r="B64" s="53" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>122</v>
@@ -4658,46 +4687,46 @@
         <v>123</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M64" s="5"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A65" s="80" t="s">
-        <v>305</v>
-      </c>
-      <c r="B65" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="C65" s="30" t="s">
-        <v>258</v>
+      <c r="A65" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B65" s="79" t="s">
+        <v>425</v>
+      </c>
+      <c r="C65" s="76" t="s">
+        <v>256</v>
       </c>
       <c r="E65" s="75" t="s">
+        <v>377</v>
+      </c>
+      <c r="F65" s="63" t="s">
+        <v>389</v>
+      </c>
+      <c r="G65" s="61" t="s">
         <v>380</v>
       </c>
-      <c r="F65" s="63" t="s">
-        <v>392</v>
-      </c>
-      <c r="G65" s="61" t="s">
-        <v>383</v>
-      </c>
       <c r="H65" s="24" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="M65" s="5"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B66" s="79" t="s">
-        <v>428</v>
-      </c>
-      <c r="C66" s="76" t="s">
-        <v>258</v>
+        <v>424</v>
+      </c>
+      <c r="C66" s="82" t="s">
+        <v>256</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>128</v>
@@ -4706,10 +4735,10 @@
         <v>129</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M66" s="5"/>
     </row>
@@ -4721,7 +4750,7 @@
         <v>427</v>
       </c>
       <c r="C67" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>130</v>
@@ -4730,7 +4759,7 @@
         <v>131</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>27</v>
@@ -4738,14 +4767,17 @@
       <c r="M67" s="5"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="B68" s="79" t="s">
-        <v>430</v>
-      </c>
-      <c r="C68" s="82" t="s">
-        <v>258</v>
+      <c r="A68" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="B68" s="85" t="s">
+        <v>303</v>
+      </c>
+      <c r="C68" s="81" t="s">
+        <v>431</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>124</v>
@@ -4754,7 +4786,7 @@
         <v>125</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>27</v>
@@ -4763,13 +4795,13 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E69" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>27</v>
@@ -4778,7 +4810,7 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4789,7 +4821,7 @@
         <v>127</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>27</v>
@@ -4798,46 +4830,46 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B71" s="52" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B72" s="79" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E72" s="58" t="s">
         <v>116</v>
       </c>
       <c r="F72" s="65" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>27</v>
@@ -4845,13 +4877,13 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B73" s="79" t="s">
         <v>422</v>
       </c>
-      <c r="B73" s="79" t="s">
-        <v>425</v>
-      </c>
       <c r="C73" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>106</v>
@@ -4860,33 +4892,33 @@
         <v>107</v>
       </c>
       <c r="G73" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B74" s="79" t="s">
         <v>421</v>
       </c>
-      <c r="B74" s="79" t="s">
-        <v>424</v>
-      </c>
       <c r="C74" s="82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F74" s="44" t="s">
         <v>134</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
@@ -4897,7 +4929,7 @@
         <v>105</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>27</v>
@@ -4905,13 +4937,13 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E76" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F76" s="40" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G76" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>27</v>
@@ -4919,16 +4951,16 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E77" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F77" s="28" t="s">
         <v>98</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
@@ -4939,7 +4971,7 @@
         <v>100</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>27</v>
@@ -4953,7 +4985,7 @@
         <v>103</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>108</v>
@@ -4961,13 +4993,13 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E80" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F80" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="F80" s="28" t="s">
-        <v>245</v>
-      </c>
       <c r="G80" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>27</v>
@@ -4975,16 +5007,16 @@
     </row>
     <row r="81" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E81" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F81" s="43" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G81" s="42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="5:8" x14ac:dyDescent="0.3">
@@ -4995,7 +5027,7 @@
         <v>63</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>27</v>
@@ -5005,7 +5037,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B20:D68">
     <sortCondition ref="D68"/>
   </sortState>
-  <phoneticPr fontId="30" type="noConversion"/>
+  <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/模组列表.xlsx
+++ b/模组列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4E5F57-58DF-4F34-A538-0BDD0A0C81EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A5B95C-F275-4F5E-BD39-19D8879E5873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5450" yWindow="0" windowWidth="20030" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="466">
   <si>
     <t>原版名称</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>AetherAspects</t>
@@ -82,1121 +82,1121 @@
   </si>
   <si>
     <t>扩展/优化</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>其他模组</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Achgrate</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>修复模组联动的一些BUG</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>GTNH维护的模组的Lib库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>1.7.10版本的Mixin总和</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>破坏性修复龙API和魔戒的冲突</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>EntityCulling-Unofficial</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>实体渲染机制优化</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：传承</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>LOTRMod</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">ChromatiCraft </t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Thaumcraft拓展 前置是DragonAPI </t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Middleearththaumaturgy</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>中土神秘学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是LOTRMod</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔戒nei附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔戒合成</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，nei全家, NEI Recipe Handlers</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Aether</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Aether</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Gilded-games-util</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Gilded-games-util</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘生物要素扫描</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>TwilightForest</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>应用能源2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>天境2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>天境要素扫描</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>以太前置库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>黑暗神秘学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>暮色森林</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>旅者之器</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘基础学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>SpecialMobs</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>特殊怪物</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>LycanitesMobsComplete</t>
   </si>
   <si>
     <t>恐怖生物</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>MoCreatures-Legacy-Final</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>更多生物分支版本</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>WitchingGadgets</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>巫师宝具</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumaturgical Knowledge</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>TravellersGear</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>WarpTheory</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘扭曲学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcarpentry</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘木匠</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘奥义</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThermalFoundation</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>热力基本</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThermalDynamics</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>热动力学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工艺</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>TofuFactoryR</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>豆腐工厂重制版</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>林业</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>光明之弓</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔法蜜蜂</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Forestry</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置是Forestry</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔法曲奇</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>混合魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>MagicalDecorations</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘装饰</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>自然魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>AdvancedThaumaturgy</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>炼金炉篦</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>高等神秘学2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代nei附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftGates</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>奥法管道</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BC</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>源质罐子统计</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Polybius</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>更多要素</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>TCBotaniaExoflame</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Talismans2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>护身符2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Machina</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘工匠</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicUtilities</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘实用工具</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic_Upholstery</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumores</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>奥能矿物</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicSanity</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>扭曲修正</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicPipes</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘管道</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，MJUtils</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，nei全家</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Additions</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘领域</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ParticleLib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Dyes</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘染料</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘力学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Nexus</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicenergistics</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘能源</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Applied Energistics 2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicalchemy</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘炼金学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicEquivalence</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>奥法置换</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumichorizons</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘视界</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicInfusion</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘注魔</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExpansion</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘膨胀</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicExploration</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘探险</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘守望者</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘启示</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔法金属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>量子魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>奥法工程学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ImmersiveEngineering</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneArteries</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>奥法献祭学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Automagy</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>自动化魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Carpenter's Blocks</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Avaritia</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>无尽贪婪</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>血魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>热力核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>CodeChickenCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>鸡块核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>木匠方块</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Carpenter's+Blocks</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>建筑核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>建筑</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是buildcraft-compat</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>植物魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>CraftArcanum</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔改</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ElectricThaum</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>电力魔法工具</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，BloodMagic，EvilCraft，Botania</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，ImmersiveEngineering</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ElecCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrial Craft 2，ElecCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>EssentialThaumaturgy</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>源质神秘学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，EssentialCraft3</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是DummyCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘电动核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Nihilo</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>无中生有</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Forbidden</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>禁忌魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ForgeMultipart</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Gadomancy</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔像秘经</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Hammerz</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>HeartWork</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>心血结晶</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>InfusionBrewing</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>注魔酿造</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>沉浸工程</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>工业时代2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>IndustrialUpgrade</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>工业升级</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Industrialcraft</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Industrialcraft</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>InventoryTweaks</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>R键整理</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑艺术之刃</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade-SlashArts</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Symcalc</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>对称度运算仪</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>奥数投射</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>等价交换</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Railcraft</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>NodalMechanics</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>节点力学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Technomancy</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Tchelper</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘研究帮助</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Tcinventoryscan</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代物品栏扫描</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Tcnodetracker</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘节点追踪</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Tainted-Magic</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>污秽魔法</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>姆亚核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Shamanry</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>巫媒</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Origin</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ParticleLib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>粒子库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>铁路</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>DummyCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>齿轮核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，DummyCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>锤子</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>OmnisCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>橘子核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Mjutils</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，PrjectE</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ExtraScepterStaff</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>独角兽权杖</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Boots</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘靴子</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Muya</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft拓展 前置Ex-Nihilo</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Localization Optimizer</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代本地化优化</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Not Enough Thaumcraft Tabs</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>无限神秘标签页</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 Tweaks</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>失落遗物学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Forgotten Relics</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Transmute Liquids</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘标签页</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>液体嬗变</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>星辉生万物重制版</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Ex-Astris-Rebirth</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Garden of Glass</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>水晶花园</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置Botania</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>FpsReducer</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Fps减速器</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Thermal热力全家，Origin</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>nei添加更多神秘合成类型显示</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘纠缠</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicBases</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicRevelations</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>AWWayofTime</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔法作物</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>区块预生成器</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>F</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Warden</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicTinkerer</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>IlluminatedBows</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>MagiaNaturalis</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>MagicCookies</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>MixedMagic</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>支持拼音搜索与 JEI 风格的关键字匹配</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneEngineering</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ElectroMagicTools</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>巫术</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Omnis Core，Multipart，CodeChicken Lib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，CodeChicken Lib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>格雷科技6</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>工艺奥秘,电力神秘</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft联动是TwilightForest,LycanitesMobsComplete,MoCreatures,SpecialMobs</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">  模组重置了NEI的注册系统会在根目录下写入缓存，模组变动一次就会重写一次。会导致加载时间变长很多。放在了可以替换模组的文件夹下。需要使用可以加载。</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>要点</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Aroma1997Core</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>AromaBackup</t>
   </si>
   <si>
     <t>Aroma系列模组核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>备份模组</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Aroma1997Core</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>EnderIO</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>高版本加载界面</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>EnderCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>末影核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>末影接口</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Angelica</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>替代optfine</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>NEI包括附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Nei合成显示扩展</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>NEI-Integration</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>原版名称</t>
@@ -1209,618 +1209,718 @@
   </si>
   <si>
     <t>前置是Thaumcraft，旧版本译名神秘守望者，还有更古早的叫Thaumic Warden都是这个模组。</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>GregTech 6</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft   Thaumcraft 4 Tweaks类似功能</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Xaeros_Minimap</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Xaero的小地图</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Omnis核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘混成</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumicHybrid</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘糅合</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，通过Mixin注入的方式修复了联动和神秘4本身的一些问题</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Integration</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘集合</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ThaumcraftAltarCull</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘祭坛稳定器渲染剔除</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，当玩家远离祭坛时，自动“剔除”稳定器方块 的渲染</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，将Thaumcraft模组的机制和要素整合进其他不原生支持 Thaumcraft 的模组里</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft 4 : Patched</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘时代4：修补</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，NemexLib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>NemexLib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Nemex库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘温泉</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic Renaissance</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘复兴</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是unimixins-all，DragonAPI ，LOTRMod，所有的材质都未实装</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Deathly Hallows</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>死亡圣器</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Botania，Witchery</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Essentia Pipes</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>管道简化</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Salis Arcana</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>奥秘之盐</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Cybersus</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔能义体</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ItemBlackListFIXED</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>物品黑名单修复版</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>合成冲突消除：修复版</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>RecipeConflict Fixer</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ChromatiFixes</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔戒：溢出修复</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是LOTRMod，修复和其他模组可能导致的工具类数组溢出</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>龙之研究前置</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>BrandonsCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Draconic-Evolution</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Hell Integrations</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘众戒</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Baubles Expanded和Baubles任选其一</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置BrandonsCore</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑西风之刃</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>LOTweakR</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元修复</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元另一个修复</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">前置是ChromatiCraft </t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>安装可否</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Bugtorch</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Gtnhlib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>中文名/注释</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Modernsplash</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Unimixins-all</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Buildcraft-compat</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Jar Checker</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>地狱合集</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>联动模组</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Trop</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicthermae</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumicmixins</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Manametalmod</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Magicbees</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Witchery</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Neiaddons</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Nechar-GTNH（NotEnoughCharacters）</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Tcneiadditions</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Lotrcrashfix</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>NeiRecipeHandlers</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>NeiLotr</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumcraft Minus Thaumcraft</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Thaumic-Errata</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，联动了Grimoire of Gaia，Automagy，Thermal Foundation</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑包括附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是SlashBlade</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，SlashBlade，SlashBlade_DarkRaven</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Magicalcrops</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>以太2包括附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>魔戒包括附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>缤纷纪元以及修复</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Industrialcraft，Tainted Magic，Electro Magic Tools（EMT）</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>神秘联动 1.1.2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>拔刀剑-暗鸦 1.1.2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>红色名字是作者反编译+修BUG后重新打包的模组。绿色名字是新加的模组后面是整合包版本号</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Chromaticraft-AIFixes（Zaifix）</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>JAOPC</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>另一版本的统一矿物</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>CarbonConfig</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Chunk+Pregenerator的核心</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是CarbonConfig</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>自动解锁所有神秘时代研究1.2.2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>chunkapi</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>endlessids</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>我看到了什么</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>wdmla</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Wawla</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>waila的fork版本</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是NEI全套</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>拓展所有ID</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>falsepatternlib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是chunkapi，falsepatternlib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>对非 libraries 模组进行版本安全的依赖处理</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>将自定义数据添加到区块的模组</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>forgelin-GTNH</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，forgelin-GTNH</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
     <t>ThaumcraftResearchTweaks</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>研究工具 1.1.6</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>WailaHarvestability</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Waila Plugins</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>1.1.6.2版本后被移除</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属，工具条件</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>waila的附属，更多显示</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>MouseTweaks</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>鼠标手势</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>forgelin库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>journeymap</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>旅行地图</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Thaumcraft，Avaritia，Botania，Applied Energistics 2，Draconic Evolution，Advanced Solar Panels移除</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>源质魔法4</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>EssentialCraft4</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>F</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ForgeMultipart库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Mjutils库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>应用能源以及附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>ExtraCells</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>更多存储单元2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Appliedenergistics2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>前置是Appliedenergistics2</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>p455w0rdslib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>p455w0rdslib库</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>WirelessCraftingTerminal</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>无线终端</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>植物魔法以及附属</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>Advanced Botany</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>高级植物学</t>
-    <phoneticPr fontId="34" type="noConversion"/>
-  </si>
-  <si>
-    <t>前置是p455w0rdslib</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>NonUpdate</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>不再有更新</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="34" type="noConversion"/>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluxedcore</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>warpbook</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>fluxed核心</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送书</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thaumicinsurgence</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘革命</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘装饰品</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1.6.8移除</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>ae2stuff</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>更多拓展</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimationAPI</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画API</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThaumcraftRecipes</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘合成</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>bdlib</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>BD库</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>modularui</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置库</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置是bdlib</t>
+    <phoneticPr fontId="37" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置是p455w0rdslib，modularui</t>
+    <phoneticPr fontId="37" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="46">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2245,291 +2345,318 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="5" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2817,8 +2944,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H125"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14"/>
+  <dimension ref="A1:H131"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="37.75" style="2" bestFit="1" customWidth="1"/>
@@ -2831,7 +2958,7 @@
     <col min="9" max="16384" width="8.9140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2857,7 +2984,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2871,7 +2998,7 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>288</v>
       </c>
@@ -2892,7 +3019,7 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>278</v>
       </c>
@@ -2915,7 +3042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>279</v>
       </c>
@@ -2941,7 +3068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>351</v>
       </c>
@@ -2964,7 +3091,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.75" customHeight="1">
+    <row r="7" spans="1:8" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>392</v>
       </c>
@@ -2987,7 +3114,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.75" customHeight="1">
+    <row r="8" spans="1:8" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>155</v>
       </c>
@@ -3013,7 +3140,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -3036,7 +3163,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>247</v>
       </c>
@@ -3059,7 +3186,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>352</v>
       </c>
@@ -3082,7 +3209,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>346</v>
       </c>
@@ -3108,7 +3235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>354</v>
       </c>
@@ -3131,7 +3258,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>406</v>
       </c>
@@ -3154,7 +3281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>355</v>
       </c>
@@ -3177,7 +3304,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>396</v>
       </c>
@@ -3200,7 +3327,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>397</v>
       </c>
@@ -3226,7 +3353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14" customHeight="1">
+    <row r="18" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="2" t="s">
         <v>238</v>
       </c>
@@ -3240,7 +3367,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
@@ -3260,7 +3387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>390</v>
       </c>
@@ -3283,7 +3410,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>143</v>
       </c>
@@ -3306,7 +3433,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.75" customHeight="1">
+    <row r="22" spans="1:8" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="56" t="s">
         <v>255</v>
       </c>
@@ -3329,7 +3456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>339</v>
       </c>
@@ -3355,7 +3482,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>356</v>
       </c>
@@ -3381,7 +3508,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>357</v>
       </c>
@@ -3405,7 +3532,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>150</v>
       </c>
@@ -3428,7 +3555,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>147</v>
       </c>
@@ -3451,7 +3578,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
@@ -3474,7 +3601,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
@@ -3497,7 +3624,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>340</v>
       </c>
@@ -3523,7 +3650,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>218</v>
       </c>
@@ -3546,7 +3673,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>164</v>
       </c>
@@ -3569,7 +3696,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>285</v>
       </c>
@@ -3592,7 +3719,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>283</v>
       </c>
@@ -3615,11 +3742,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B35" s="86" t="s">
+      <c r="B35" s="85" t="s">
         <v>426</v>
       </c>
       <c r="C35" s="30" t="s">
@@ -3641,7 +3768,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>171</v>
       </c>
@@ -3664,7 +3791,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>76</v>
       </c>
@@ -3687,11 +3814,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B38" s="87" t="s">
+      <c r="B38" s="86" t="s">
         <v>429</v>
       </c>
       <c r="C38" s="35" t="s">
@@ -3710,7 +3837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>244</v>
       </c>
@@ -3736,7 +3863,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>137</v>
       </c>
@@ -3759,7 +3886,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>187</v>
       </c>
@@ -3782,7 +3909,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>185</v>
       </c>
@@ -3808,7 +3935,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>189</v>
       </c>
@@ -3831,7 +3958,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>330</v>
       </c>
@@ -3854,15 +3981,18 @@
         <v>311</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="29" t="s">
-        <v>254</v>
+      <c r="C45" s="80" t="s">
+        <v>258</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>453</v>
       </c>
       <c r="E45" t="s">
         <v>358</v>
@@ -3877,11 +4007,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B46" s="87" t="s">
+      <c r="B46" s="86" t="s">
         <v>430</v>
       </c>
       <c r="C46" s="44" t="s">
@@ -3900,7 +4030,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>55</v>
       </c>
@@ -3923,7 +4053,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
@@ -3946,7 +4076,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
@@ -3969,7 +4099,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>315</v>
       </c>
@@ -3992,7 +4122,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>222</v>
       </c>
@@ -4015,7 +4145,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>214</v>
       </c>
@@ -4038,7 +4168,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>215</v>
       </c>
@@ -4061,7 +4191,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -4084,11 +4214,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B55" s="85" t="s">
+      <c r="B55" s="84" t="s">
         <v>332</v>
       </c>
       <c r="C55" s="29" t="s">
@@ -4107,7 +4237,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>51</v>
       </c>
@@ -4130,7 +4260,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>68</v>
       </c>
@@ -4153,7 +4283,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>66</v>
       </c>
@@ -4166,8 +4296,8 @@
       <c r="E58" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F58" s="27" t="s">
-        <v>81</v>
+      <c r="F58" s="94" t="s">
+        <v>452</v>
       </c>
       <c r="G58" s="15" t="s">
         <v>254</v>
@@ -4176,7 +4306,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>71</v>
       </c>
@@ -4199,7 +4329,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>60</v>
       </c>
@@ -4222,7 +4352,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>42</v>
       </c>
@@ -4245,7 +4375,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>57</v>
       </c>
@@ -4268,7 +4398,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>410</v>
       </c>
@@ -4291,7 +4421,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>420</v>
       </c>
@@ -4314,7 +4444,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>423</v>
       </c>
@@ -4337,11 +4467,11 @@
         <v>375</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="79" t="s">
         <v>299</v>
       </c>
-      <c r="B66" s="84" t="s">
+      <c r="B66" s="92" t="s">
         <v>300</v>
       </c>
       <c r="C66" s="80" t="s">
@@ -4363,15 +4493,15 @@
         <v>249</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>436</v>
       </c>
       <c r="B67" s="78" t="s">
         <v>437</v>
       </c>
-      <c r="C67" s="91" t="s">
-        <v>446</v>
+      <c r="C67" s="90" t="s">
+        <v>445</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>129</v>
@@ -4386,15 +4516,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B68" s="78" t="s">
         <v>444</v>
       </c>
-      <c r="B68" s="78" t="s">
+      <c r="C68" s="90" t="s">
         <v>445</v>
-      </c>
-      <c r="C68" s="91" t="s">
-        <v>446</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>123</v>
@@ -4409,7 +4539,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B69" s="78" t="s">
+        <v>448</v>
+      </c>
+      <c r="C69" s="91" t="s">
+        <v>254</v>
+      </c>
       <c r="E69" s="2" t="s">
         <v>303</v>
       </c>
@@ -4423,13 +4562,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B70" s="78" t="s">
+        <v>449</v>
+      </c>
+      <c r="C70" s="91" t="s">
+        <v>254</v>
+      </c>
       <c r="E70" s="57" t="s">
         <v>125</v>
       </c>
@@ -4443,14 +4585,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B71" s="51" t="s">
-        <v>401</v>
-      </c>
-      <c r="C71" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="B71" s="78" t="s">
+        <v>457</v>
+      </c>
+      <c r="C71" s="91" t="s">
         <v>254</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -4466,17 +4608,16 @@
         <v>305</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="B72" s="78" t="s">
-        <v>402</v>
-      </c>
-      <c r="C72" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="D72" s="4"/>
+        <v>461</v>
+      </c>
+      <c r="C72" s="95" t="s">
+        <v>254</v>
+      </c>
       <c r="E72" s="57" t="s">
         <v>115</v>
       </c>
@@ -4490,14 +4631,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B73" s="78" t="s">
-        <v>419</v>
-      </c>
-      <c r="C73" s="81" t="s">
+        <v>462</v>
+      </c>
+      <c r="B73" s="100" t="s">
+        <v>463</v>
+      </c>
+      <c r="C73" s="95" t="s">
         <v>254</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -4513,16 +4654,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="B74" s="78" t="s">
-        <v>418</v>
-      </c>
-      <c r="C74" s="81" t="s">
-        <v>254</v>
-      </c>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E74" s="2" t="s">
         <v>253</v>
       </c>
@@ -4536,7 +4668,13 @@
         <v>296</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
       <c r="E75" s="2" t="s">
         <v>103</v>
       </c>
@@ -4550,13 +4688,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B76" s="51" t="s">
+        <v>401</v>
+      </c>
+      <c r="C76" s="29" t="s">
+        <v>254</v>
+      </c>
       <c r="E76" s="2" t="s">
         <v>362</v>
       </c>
@@ -4570,19 +4711,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B77" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="C77" s="88" t="s">
-        <v>254</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>435</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="B77" s="78" t="s">
+        <v>402</v>
+      </c>
+      <c r="C77" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" s="4"/>
       <c r="E77" s="2" t="s">
         <v>260</v>
       </c>
@@ -4596,14 +4735,14 @@
         <v>270</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="B78" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C78" s="34" t="s">
+        <v>416</v>
+      </c>
+      <c r="B78" s="78" t="s">
+        <v>419</v>
+      </c>
+      <c r="C78" s="81" t="s">
         <v>254</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -4619,18 +4758,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B79" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="C79" s="34" t="s">
-        <v>254</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>443</v>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B79" s="78" t="s">
+        <v>418</v>
+      </c>
+      <c r="C79" s="81" t="s">
+        <v>254</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>101</v>
@@ -4645,7 +4781,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E80" s="2" t="s">
         <v>239</v>
       </c>
@@ -4659,9 +4795,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -4679,15 +4815,18 @@
         <v>343</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>2</v>
+        <v>432</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="C82" s="90" t="s">
-        <v>254</v>
+        <v>433</v>
+      </c>
+      <c r="C82" s="87" t="s">
+        <v>254</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>435</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>61</v>
@@ -4702,158 +4841,156 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="89" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F83" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="G83" s="93" t="s">
+        <v>254</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="C84" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F84" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="G84" s="99" t="s">
+        <v>254</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B85" s="97" t="s">
+        <v>455</v>
+      </c>
+      <c r="C85" s="98" t="s">
+        <v>254</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" s="89" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="88" t="s">
         <v>441</v>
       </c>
-      <c r="B83" s="26" t="s">
+      <c r="B89" s="26" t="s">
         <v>442</v>
       </c>
-      <c r="C83" s="90" t="s">
-        <v>446</v>
-      </c>
-      <c r="D83"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="3" t="s">
+      <c r="C89" s="89" t="s">
+        <v>445</v>
+      </c>
+      <c r="D89"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="2" t="s">
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B86" s="27" t="s">
+      <c r="B92" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="C86" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D86" s="2" t="s">
+      <c r="C92" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="2" t="s">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B93" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B88" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B89" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B90" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C90" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B93" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="10" t="s">
         <v>254</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C94" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C94" s="17" t="s">
         <v>254</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C95" s="16" t="s">
         <v>254</v>
@@ -4862,316 +4999,400 @@
         <v>131</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="3" t="s">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B96" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="2" t="s">
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B98" s="27" t="s">
+      <c r="B104" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C98" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D98" s="4"/>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="2" t="s">
+      <c r="C104" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D104" s="4"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B99" s="27" t="s">
+      <c r="B105" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C105" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="2" t="s">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B100" s="27" t="s">
+      <c r="B106" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C100" s="19" t="s">
+      <c r="C106" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D106" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="55" t="s">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="55" t="s">
         <v>276</v>
       </c>
-      <c r="B101" s="55"/>
-      <c r="C101" s="55"/>
-      <c r="D101" s="55"/>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="2" t="s">
+      <c r="B107" s="55"/>
+      <c r="C107" s="55"/>
+      <c r="D107" s="55"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B102" s="27" t="s">
+      <c r="B108" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="C102" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="D102" s="2" t="s">
+      <c r="C108" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103"/>
-      <c r="B103"/>
-      <c r="C103"/>
-      <c r="D103"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="3" t="s">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="2" t="s">
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="27" t="s">
+      <c r="B111" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C105" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D105" s="4"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="2" t="s">
+      <c r="C111" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D111" s="4"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B106" s="27" t="s">
+      <c r="B112" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C106" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="C112" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="2" t="s">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B107" s="27" t="s">
+      <c r="B113" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C107" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D107" s="2" t="s">
+      <c r="C113" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="3" t="s">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B110" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B111" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="C111" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B112" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B113" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B116" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B117" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B118" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B119" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B116" s="45" t="s">
+      <c r="B122" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="C116" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D116" s="2" t="s">
+      <c r="C122" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
-      <c r="A117" s="2" t="s">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B117" s="45" t="s">
+      <c r="B123" s="45" t="s">
         <v>347</v>
       </c>
-      <c r="C117" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="D117" s="2" t="s">
+      <c r="C123" s="46" t="s">
+        <v>254</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="2" t="s">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B118" s="45" t="s">
+      <c r="B124" s="45" t="s">
         <v>348</v>
       </c>
-      <c r="C118" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="D118" s="2" t="s">
+      <c r="C124" s="46" t="s">
+        <v>254</v>
+      </c>
+      <c r="D124" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="3" t="s">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" s="2" t="s">
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B121" s="28" t="s">
+      <c r="B127" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="C121" s="31" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="61" t="s">
+      <c r="C127" s="31" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="61" t="s">
         <v>379</v>
       </c>
-      <c r="B122" s="63" t="s">
+      <c r="B128" s="63" t="s">
         <v>387</v>
       </c>
-      <c r="C122" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="D122" s="2" t="s">
+      <c r="C128" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="2" t="s">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B123" s="49" t="s">
+      <c r="B129" s="49" t="s">
         <v>345</v>
       </c>
-      <c r="C123" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="D123" s="2" t="s">
+      <c r="C129" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="D129" s="2" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
-      <c r="A124" s="2" t="s">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B124" s="48" t="s">
+      <c r="B130" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="C124" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="D124" s="2" t="s">
+      <c r="C130" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="D130" s="2" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
-      <c r="A125" s="56" t="s">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="56" t="s">
         <v>179</v>
       </c>
-      <c r="B125" s="27" t="s">
+      <c r="B131" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C125" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="D125" s="23" t="s">
+      <c r="C131" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D131" s="23" t="s">
         <v>380</v>
       </c>
     </row>
@@ -5179,7 +5400,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B20:D68">
     <sortCondition ref="D68"/>
   </sortState>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
